--- a/Data Files/AppData.xlsx
+++ b/Data Files/AppData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03d9f77266578c72/Documents/Desktop/Arjun/KatalonStudio_EventHub/EventHub/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_F25DC773A252ABDACC1048DD79D857A05BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08FC4CD3-DC1D-4DED-85B5-C1272016841C}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_F25DC773A252ABDACC1048DD79D857A05BDE58E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8343DAFA-4EBB-48D4-B1A1-581A590EABB7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SignUpDetails" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -88,7 +88,94 @@
     <t>EmailID</t>
   </si>
   <si>
-    <t>arjun@gmail.com</t>
+    <t>user_1776589518114@gmail.com</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Mrs</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Andhra</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Chittoor</t>
+  </si>
+  <si>
+    <t>krEnkAEo</t>
+  </si>
+  <si>
+    <t>user_1776590439077@gmail.com</t>
+  </si>
+  <si>
+    <t>IJOerxki</t>
+  </si>
+  <si>
+    <t>pxunYOPh</t>
+  </si>
+  <si>
+    <t>vELgWOZM</t>
+  </si>
+  <si>
+    <t>cflbQlxH</t>
+  </si>
+  <si>
+    <t>UVSnKGhC</t>
+  </si>
+  <si>
+    <t>yrChcrwf</t>
+  </si>
+  <si>
+    <t>9958284833</t>
+  </si>
+  <si>
+    <t>hkssnQeV</t>
+  </si>
+  <si>
+    <t>user_1776591988554@gmail.com</t>
+  </si>
+  <si>
+    <t>HtzaaBux</t>
+  </si>
+  <si>
+    <t>mtQlpjju</t>
+  </si>
+  <si>
+    <t>XXQpdpCN</t>
+  </si>
+  <si>
+    <t>voesubGj</t>
+  </si>
+  <si>
+    <t>axBfJxfh</t>
+  </si>
+  <si>
+    <t>YteWXREG</t>
+  </si>
+  <si>
+    <t>9521625341</t>
   </si>
 </sst>
 </file>
@@ -142,10 +229,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -473,9 +556,86 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>42</v>
+      </c>
       <c r="C2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E2" s="0">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="G2" s="0">
+        <v>1992</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="R2" s="0">
+        <v>560037</v>
+      </c>
+      <c r="S2" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="C3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="Q3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="R3" s="0">
+        <v>517192</v>
       </c>
     </row>
   </sheetData>

--- a/Data Files/AppData.xlsx
+++ b/Data Files/AppData.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>Name</t>
   </si>
@@ -176,6 +176,33 @@
   </si>
   <si>
     <t>9521625341</t>
+  </si>
+  <si>
+    <t>FsrkattI</t>
+  </si>
+  <si>
+    <t>user_1776592151747@gmail.com</t>
+  </si>
+  <si>
+    <t>MjshyaVM</t>
+  </si>
+  <si>
+    <t>sSklfMcU</t>
+  </si>
+  <si>
+    <t>lzXGpijE</t>
+  </si>
+  <si>
+    <t>FjOkIDji</t>
+  </si>
+  <si>
+    <t>mnKFUmYm</t>
+  </si>
+  <si>
+    <t>FhTzCeJv</t>
+  </si>
+  <si>
+    <t>9740043956</t>
   </si>
 </sst>
 </file>
@@ -558,16 +585,16 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>21</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E2" s="0">
         <v>30</v>
@@ -585,19 +612,19 @@
         <v>25</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="O2" t="s" s="0">
         <v>26</v>
@@ -612,7 +639,7 @@
         <v>560037</v>
       </c>
       <c r="S2" t="s" s="0">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
